--- a/EKG_Kalite_Yönetim_Sistemi/13_Giriş Lojistiği ve Depolama/02_ILG2 - Tedarik Alarmı, EDI ve Protokoller/EKG-LOJ-TLM-03_edi_kullanim_talimati_ve_yedek_cozum_plani.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/13_Giriş Lojistiği ve Depolama/02_ILG2 - Tedarik Alarmı, EDI ve Protokoller/EKG-LOJ-TLM-03_edi_kullanim_talimati_ve_yedek_cozum_plani.xlsx
@@ -795,7 +795,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-TLM-03&amp;C&amp;"Arial,Regular"&amp;11EDI Kullanım Talimatı ve Yedek Çözüm Planı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 28.05.2026 | Revizyon: 27.08.2026
+Revizyon nedeni: EDI yedek erişim, mesaj teyidi, düzeltme ve kurtarma mutabakatı adımları düzenlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -963,7 +964,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-TLM-03&amp;C&amp;"Arial,Regular"&amp;11EDI Kullanım Talimatı ve Yedek Çözüm Planı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 28.05.2026 | Revizyon: 27.08.2026
+Revizyon nedeni: EDI yedek erişim, mesaj teyidi, düzeltme ve kurtarma mutabakatı adımları düzenlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1157,7 +1159,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-TLM-03&amp;C&amp;"Arial,Regular"&amp;11EDI Kullanım Talimatı ve Yedek Çözüm Planı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 28.05.2026 | Revizyon: 27.08.2026
+Revizyon nedeni: EDI yedek erişim, mesaj teyidi, düzeltme ve kurtarma mutabakatı adımları düzenlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>